--- a/course allocation.xlsx
+++ b/course allocation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugma\Documents\antigravity\ems ppsu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752BC095-4E85-43C9-AB62-77CAA615456D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E90C35-463A-4886-B6C1-5B023E75B0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{8F33EAFB-CD91-4B14-9073-932E749FF54F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{8F33EAFB-CD91-4B14-9073-932E749FF54F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="41">
   <si>
     <t xml:space="preserve">Sem </t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>ASH</t>
+  </si>
+  <si>
+    <t>ypm</t>
   </si>
 </sst>
 </file>
@@ -620,6 +623,12 @@
       <c r="E5" t="s">
         <v>22</v>
       </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
       <c r="H5" t="s">
         <v>23</v>
       </c>

--- a/course allocation.xlsx
+++ b/course allocation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yugma\Documents\antigravity\ems ppsu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\exam\Exam-Management-Automation-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E90C35-463A-4886-B6C1-5B023E75B0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B4458C-5E17-40C7-862B-B083077D399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{8F33EAFB-CD91-4B14-9073-932E749FF54F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="42">
   <si>
     <t xml:space="preserve">Sem </t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>ypm</t>
+  </si>
+  <si>
+    <t>yug</t>
   </si>
 </sst>
 </file>
@@ -595,13 +598,13 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
         <v>19</v>
